--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260828.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260828.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>75,407</t>
+          <t>75,907</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.96%</t>
+          <t>10.88%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>31,196</t>
+          <t>31,496</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.40%</t>
+          <t>10.22%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>87,425</t>
+          <t>88,225</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.22%</t>
+          <t>8.07%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>34,355</t>
+          <t>34,655</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.46%</t>
+          <t>7.44%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>189,056</t>
+          <t>190,556</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.51%</t>
+          <t>5.55%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>100,491</t>
+          <t>101,291</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.24%</t>
+          <t>4.34%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>47,395</t>
+          <t>47,795</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
@@ -765,56 +765,56 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>108,966</t>
+          <t>109,866</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.45%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>HUBB US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>安柏</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>57,059</t>
+          <t>18,879</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>HUBB US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>安柏</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>18,679</t>
+          <t>57,559</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>113,383</t>
+          <t>114,283</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>52,527</t>
+          <t>52,927</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>21,731</t>
+          <t>21,931</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>132,001</t>
+          <t>133,101</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>23,504</t>
+          <t>23,704</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>60,303</t>
+          <t>60,803</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -963,100 +963,100 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>35,580</t>
+          <t>35,880</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>49,610</t>
+          <t>48,536</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>48,136</t>
+          <t>50,010</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>74,501</t>
+          <t>48,860</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>48,460</t>
+          <t>75,201</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>92,063</t>
+          <t>92,763</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1095,56 +1095,56 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>31,410</t>
+          <t>31,710</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>29,445</t>
+          <t>45,927</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>45,527</t>
+          <t>29,645</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>21,558</t>
+          <t>21,658</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1183,51 +1183,51 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>26,669</t>
+          <t>26,869</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>10,937</t>
+          <t>20,209</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>20,009</t>
+          <t>11,037</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>141,345</t>
+          <t>73,274</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,44 +1261,44 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>72,674</t>
+          <t>8,704</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>8,704</t>
+          <t>29,514</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>12,752</t>
+          <t>12,852</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,22 +1327,22 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>29,314</t>
+          <t>142,545</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1364,51 +1364,51 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>4,721</t>
+          <t>29,891</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>29,691</t>
+          <t>4,721</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>10,246</t>
+          <t>10,346</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>24,881</t>
+          <t>25,181</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>42,083</t>
+          <t>42,383</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>15,527</t>
+          <t>15,727</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>12,924</t>
+          <t>13,024</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>91,502</t>
+          <t>92,302</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>6,527</t>
+          <t>6,627</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>22,719</t>
+          <t>22,919</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7,721</t>
+          <t>7,821</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>17,853</t>
+          <t>17,953</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>37,061</t>
+          <t>37,361</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>135,761,436</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
